--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_316_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_316_R32.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2927</v>
+        <v>7.2061</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6678</v>
+        <v>7.5812</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3751</v>
@@ -610,10 +610,10 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8452</v>
+        <v>-0.9318</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0474</v>
+        <v>-0.0391</v>
       </c>
       <c r="U2" t="n">
         <v>-0.8927</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1961</v>
+        <v>2.4805</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2758</v>
+        <v>3.661</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0797</v>
+        <v>-1.1805</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4171</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6884</v>
+        <v>-0.4039</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0553</v>
+        <v>0.4406</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7437</v>
+        <v>-0.8445</v>
       </c>
       <c r="V3" t="n">
         <v>1.214</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.492</v>
+        <v>0.4552</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7435</v>
+        <v>0.2776</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2514</v>
+        <v>0.1776</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7157</v>
+        <v>-0.9523</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2483</v>
+        <v>-1.839</v>
       </c>
       <c r="I4" t="n">
-        <v>1.964</v>
+        <v>0.8867</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4023</v>
+        <v>0.4779</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6687</v>
+        <v>-0.1478</v>
       </c>
       <c r="L4" t="n">
-        <v>2.071</v>
+        <v>0.6257</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6866</v>
+        <v>-1.4303</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5796</v>
+        <v>-1.6913</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.107</v>
+        <v>0.261</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4556</v>
+        <v>0.2478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4288</v>
+        <v>0.0316</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8843</v>
+        <v>0.2161</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3871</v>
+        <v>0.357</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5947</v>
+        <v>1.5076</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2076</v>
+        <v>-1.1506</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3511</v>
+        <v>0.7157</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3047</v>
+        <v>-1.2483</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6558</v>
+        <v>1.964</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4058</v>
+        <v>1.4023</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1176</v>
+        <v>-0.6687</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2882</v>
+        <v>2.071</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0547</v>
+        <v>-0.6866</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4223</v>
+        <v>-0.5796</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6323</v>
+        <v>-0.107</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.5906</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1928</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.7835</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.8556</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.4639</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1889</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.6528</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-1.3558</v>
-      </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1079</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2689</v>
+        <v>1.3155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1776</v>
+        <v>-1.2076</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9523</v>
+        <v>0.3511</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.839</v>
+        <v>-0.3047</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8867</v>
+        <v>0.6558</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4779</v>
+        <v>1.4058</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1478</v>
+        <v>0.1176</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6257</v>
+        <v>1.2882</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4303</v>
+        <v>-1.0547</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6913</v>
+        <v>-0.4223</v>
       </c>
       <c r="O6" t="n">
-        <v>0.261</v>
+        <v>-0.6323</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2987</v>
+        <v>-0.7431</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5149</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2161</v>
+        <v>-0.6528</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2779</v>
+        <v>-1.3826</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2704</v>
+        <v>0.1559</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0075</v>
+        <v>-1.5385</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1249</v>
+        <v>-0.8393</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9604</v>
+        <v>-1.5654</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1644</v>
+        <v>0.7261</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0167</v>
+        <v>1.1274</v>
       </c>
       <c r="K7" t="n">
-        <v>0.091</v>
+        <v>0.6624</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1077</v>
+        <v>0.465</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1082</v>
+        <v>-1.9667</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0514</v>
+        <v>-2.2278</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0568</v>
+        <v>0.261</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.615</v>
+        <v>0.9928</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0657</v>
+        <v>0.3659</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4507</v>
+        <v>0.6269</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5663</v>
+        <v>-1.5065</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2294</v>
+        <v>1.2798</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3368</v>
+        <v>-2.7863</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8393</v>
+        <v>-1.0891</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5654</v>
+        <v>1.2832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7261</v>
+        <v>-2.3724</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1274</v>
+        <v>0.9344</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6624</v>
+        <v>2.4101</v>
       </c>
       <c r="L8" t="n">
-        <v>0.465</v>
+        <v>-1.4757</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9667</v>
+        <v>-2.0235</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2278</v>
+        <v>-1.1269</v>
       </c>
       <c r="O8" t="n">
-        <v>0.261</v>
+        <v>-0.8966</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8092</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0193</v>
+        <v>0.2912</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8285</v>
+        <v>-0.9379</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
         <v>1.214</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2862</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9589</v>
+        <v>-1.7258</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8946</v>
+        <v>-0.7855</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8535</v>
+        <v>-0.9402</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0891</v>
+        <v>-2.1249</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2832</v>
+        <v>-0.9604</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3724</v>
+        <v>-1.1644</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9344</v>
+        <v>-1.0167</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4101</v>
+        <v>0.091</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4757</v>
+        <v>-1.1077</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0235</v>
+        <v>-1.1082</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1269</v>
+        <v>-1.0514</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8966</v>
+        <v>-0.0568</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0991</v>
+        <v>0.1672</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.094</v>
+        <v>0.5507</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0051</v>
+        <v>-0.3835</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2773</v>
+        <v>-3.4448</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7712</v>
+        <v>-1.1067</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5061</v>
+        <v>-2.338</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1761</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7095</v>
+        <v>0.123</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6642</v>
+        <v>0.0002</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5908</v>
+        <v>-5.8215</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3055</v>
+        <v>-3.4353</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2854</v>
+        <v>-2.3862</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7434</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9748</v>
+        <v>0.7442</v>
       </c>
       <c r="T11" t="n">
-        <v>0.767</v>
+        <v>0.6372</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2862</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.394600000000001</v>
+        <v>-3.274499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.331</v>
+        <v>10.4511</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.7255</v>
+        <v>-13.7254</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0627</v>
@@ -1369,7 +1369,7 @@
         <v>5.7422</v>
       </c>
       <c r="L12" t="n">
-        <v>2.943100000000002</v>
+        <v>2.9431</v>
       </c>
       <c r="M12" t="n">
         <v>-14.7481</v>
@@ -1390,10 +1390,10 @@
         <v>18.5562</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1614</v>
+        <v>-1.0411</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2607</v>
+        <v>2.3808</v>
       </c>
       <c r="U12" t="n">
         <v>-3.4221</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.082</v>
+        <v>4.3515</v>
       </c>
       <c r="E13" t="n">
-        <v>4.243</v>
+        <v>4.0071</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.161</v>
+        <v>0.3444</v>
       </c>
       <c r="G13" t="n">
         <v>3.7975</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3721</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6528</v>
+        <v>0.4169</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2807</v>
+        <v>0.2247</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2663</v>
+        <v>3.7324</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5371</v>
+        <v>3.6551</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2708</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3.456</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6383</v>
+        <v>-0.1722</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2003</v>
+        <v>-0.0824</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.438</v>
+        <v>-0.0898</v>
       </c>
       <c r="V14" t="n">
         <v>1.6083</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5028</v>
+        <v>2.4661</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4999</v>
+        <v>1.8664</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9971</v>
+        <v>0.5997</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3402</v>
+        <v>0.9449</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9988</v>
+        <v>2.8654</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3414</v>
+        <v>-1.9205</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0944</v>
+        <v>1.1559</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4319</v>
+        <v>3.3309</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6625</v>
+        <v>-2.175</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7542</v>
+        <v>-0.211</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4331</v>
+        <v>-0.4655</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3211</v>
+        <v>0.2545</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6264</v>
+        <v>0.2504</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4208</v>
+        <v>0.1535</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2056</v>
+        <v>0.0969</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5361</v>
+        <v>3.3584</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1444</v>
+        <v>4.0363</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8255</v>
+        <v>2.3518</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8529</v>
+        <v>3.146</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0274</v>
+        <v>-0.7942</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8476</v>
+        <v>1.3402</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7489</v>
+        <v>0.9988</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5966</v>
+        <v>0.3414</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7304</v>
+        <v>2.0944</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0203</v>
+        <v>1.4319</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7101</v>
+        <v>0.6625</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8828</v>
+        <v>-0.7542</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7692</v>
+        <v>-0.4331</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1136</v>
+        <v>-0.3211</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4933</v>
+        <v>0.4755</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1404</v>
+        <v>0.067</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6471</v>
+        <v>0.4086</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2836</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4254</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7129</v>
+        <v>2.0721</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6652</v>
+        <v>2.617</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9523</v>
+        <v>-0.5448</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4282</v>
+        <v>1.8476</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1573</v>
+        <v>-0.7489</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5855</v>
+        <v>2.5966</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4659</v>
+        <v>2.7304</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.0203</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6257</v>
+        <v>2.7101</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8942</v>
+        <v>-0.8828</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7692</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2112</v>
+        <v>-0.1136</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2133</v>
+        <v>0.74</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1993</v>
+        <v>0.9045</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0141</v>
+        <v>-0.1645</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6969</v>
+        <v>1.3312</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5125</v>
+        <v>2.1934</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1844</v>
+        <v>-0.8622</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9449</v>
+        <v>-0.4282</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8654</v>
+        <v>0.1573</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9205</v>
+        <v>-0.5855</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1559</v>
+        <v>1.4659</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3309</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.175</v>
+        <v>0.6257</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.211</v>
+        <v>-1.8942</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4655</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2545</v>
+        <v>-1.2112</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5188</v>
+        <v>0.8316</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2003</v>
+        <v>0.7275</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3185</v>
+        <v>0.1041</v>
       </c>
       <c r="V18" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.0363</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2573</v>
+        <v>-1.308</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.872</v>
+        <v>-0.0463</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3854</v>
+        <v>-1.2617</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0432</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3765</v>
+        <v>0.5729</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1256</v>
+        <v>0.7</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2508</v>
+        <v>-0.1272</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2816</v>
+        <v>-2.6189</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7642</v>
+        <v>-2.2923</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5174</v>
+        <v>-0.3265</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7604</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4336</v>
+        <v>0.2291</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2385</v>
+        <v>0.4294</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1528</v>
+        <v>-5.6246</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3432</v>
+        <v>-1.815</v>
       </c>
       <c r="F21" t="n">
         <v>-3.8095</v>
@@ -2092,10 +2092,10 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4233</v>
+        <v>0.9515</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2072</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U21" t="n">
         <v>0.2161</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.394700000000001</v>
+        <v>6.7536</v>
       </c>
       <c r="E22" t="n">
-        <v>13.3312</v>
+        <v>13.3314</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.936500000000001</v>
+        <v>-6.577500000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>6.0628</v>
+        <v>6.062799999999999</v>
       </c>
       <c r="H22" t="n">
         <v>5.827900000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2347000000000004</v>
+        <v>0.2346999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>14.7481</v>
@@ -2152,7 +2152,7 @@
         <v>3.178000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.685400000000001</v>
+        <v>-8.6854</v>
       </c>
       <c r="N22" t="n">
         <v>-5.7422</v>
@@ -2170,13 +2170,13 @@
         <v>10.438</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1612</v>
+        <v>4.5204</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4222</v>
+        <v>3.4221</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2608</v>
+        <v>1.0983</v>
       </c>
       <c r="V22" t="n">
         <v>4.2888</v>
